--- a/artfynd/A 42558-2022 artfynd.xlsx
+++ b/artfynd/A 42558-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42558-2022 artfynd.xlsx
+++ b/artfynd/A 42558-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,133 +814,6 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>109324914</v>
-      </c>
-      <c r="B3" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Lopplummer</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tallbacken, Tallbacken, Nittkvarn, Dlr</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>484724.8470640765</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6662371.064417111</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Grangärde</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett fint bestånd med lopplummer i barrblandskog</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42558-2022 artfynd.xlsx
+++ b/artfynd/A 42558-2022 artfynd.xlsx
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">

--- a/artfynd/A 42558-2022 artfynd.xlsx
+++ b/artfynd/A 42558-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,6 +814,133 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>109324914</v>
+      </c>
+      <c r="B3" t="n">
+        <v>95511</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lopplummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Huperzia selago</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tallbacken, Tallbacken, Nittkvarn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>484724.8470640765</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6662371.064417111</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett fint bestånd med lopplummer i barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42558-2022 artfynd.xlsx
+++ b/artfynd/A 42558-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>104127009</v>
       </c>
       <c r="B2" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484738.795735718</v>
+        <v>484739</v>
       </c>
       <c r="R2" t="n">
-        <v>6662361.530303407</v>
+        <v>6662361</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,19 +746,9 @@
           <t>2022-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -819,12 +804,7 @@
         <v>109324914</v>
       </c>
       <c r="B3" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,19 +816,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -860,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484724.8470640765</v>
+        <v>484725</v>
       </c>
       <c r="R3" t="n">
-        <v>6662371.064417111</v>
+        <v>6662371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
